--- a/AAII_Financials/Quarterly/TTNDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTNDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
   <si>
     <t>TTNDY</t>
   </si>
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -684,103 +684,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,47 +831,53 @@
       <c r="P8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S8" s="3">
         <v>5606200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4205700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3938500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3728200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>3590400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3430800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3182000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2881600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2794800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2685700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2474000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2503000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -906,47 +920,53 @@
       <c r="P9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="3">
         <v>3450200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2608600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2448600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2325500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2249400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2157200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2011600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1825800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1778300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1716900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1647700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1592600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1616800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,47 +1009,53 @@
       <c r="P10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S10" s="3">
         <v>2156000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1597100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1489900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1402700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1341000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1273600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1170400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1055800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1016500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>968800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>916300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>881400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>886200</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,8 +1085,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,47 +1131,53 @@
       <c r="P12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" s="3">
         <v>195700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>120900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>121200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>108600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>103500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>99100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>86400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>77200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>76200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>71000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>62300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>65500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>61300</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1225,8 +1259,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1269,11 +1309,11 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1293,11 +1333,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
@@ -1308,8 +1348,14 @@
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1352,11 +1398,11 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1391,8 +1437,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,8 +1471,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1463,47 +1517,53 @@
       <c r="P17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" s="3">
         <v>5083600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3823300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3556900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3396400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3251600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3136900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2888100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2645600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2538400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2480200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2340100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2287500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2307000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,47 +1606,53 @@
       <c r="P18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" s="3">
         <v>522600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>382400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>381600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>331800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>338800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>293900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>293900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>236000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>256400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>205500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>223900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>186500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>196000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,8 +1682,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,47 +1728,53 @@
       <c r="P20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" s="3">
         <v>-17600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-26200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-27100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-25100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-19600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-18400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-11800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1743,47 +1817,53 @@
       <c r="P21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" s="3">
         <v>737100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>528300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>524200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>462600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>442300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>393500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>392300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>325400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>254500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>284400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>232500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>266800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1826,11 +1906,11 @@
       <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1838,11 +1918,11 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>10</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>10</v>
@@ -1856,17 +1936,23 @@
       <c r="Z22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC22" s="3">
         <v>10300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>13200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1909,47 +1995,53 @@
       <c r="P23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23" s="3">
         <v>505000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>356200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>354500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>306800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>319200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>275400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>282100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>223400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>246700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>193400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>213600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>173400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>176900</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1992,47 +2084,53 @@
       <c r="P24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S24" s="3">
         <v>35700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>24600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>24600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>21700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>21400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>20700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>16000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>19000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>14800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>16400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>18100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>14700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,8 +2212,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2158,47 +2262,53 @@
       <c r="P26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S26" s="3">
         <v>469400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>331600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>329900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>285100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>297800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>254800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>266100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>204400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>231900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>176900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>195500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>158600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>163900</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2241,47 +2351,53 @@
       <c r="P27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S27" s="3">
         <v>469200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>331600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>329900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>285000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>297700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>254700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>266000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>204400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>231900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>177000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>195700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>158700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>164100</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,11 +2529,11 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2446,8 +2568,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,8 +2746,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2656,47 +2796,53 @@
       <c r="P32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S32" s="3">
         <v>17600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>26200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>27100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>25100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>19600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>18400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>11800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>12600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>9700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>12100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2739,47 +2885,53 @@
       <c r="P33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S33" s="3">
         <v>469200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>331600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>329900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>285000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>297700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>254700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>266000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>204400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>231900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>177000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>195700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>158700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>164100</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,8 +3013,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2905,135 +3063,147 @@
       <c r="P35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S35" s="3">
         <v>469200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>331600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>329900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>285000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>297700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>254700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>266000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>204400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>231900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>177000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>195700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>158700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>164100</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,755 +3266,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1889200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1889200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1677700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1677700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1608400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1608400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1232300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1232300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1226500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1226500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>953200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>953200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1485100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1485100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1428900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1533900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1714900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1411800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1205600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1103900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>863100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>863500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>818100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>804700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>743800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>774600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>725200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>690400</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>235200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>235200</v>
+      </c>
+      <c r="F42" s="3">
         <v>225300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>225300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>192300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>192300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>223200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>223200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>208800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>208800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>218800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>218800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>234300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>234300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>262700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>17800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>16400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>24600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>25800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>32800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>45500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>32300</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>1000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2477500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2477500</v>
+      </c>
+      <c r="F43" s="3">
         <v>2044600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2044600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2625800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2625800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2022500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2022500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2438800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2438800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1834700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1834700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2056900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2056900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1690300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1415600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1656400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1280400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1414000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1161000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1267000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1154400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1145100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>977300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1011300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>887500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>938300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4315100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4315100</v>
+      </c>
+      <c r="F44" s="3">
         <v>4451900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>4451900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>4293000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>4293000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>4076200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>4076200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>4026700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4026700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>4098200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>4098200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4580800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>4580800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5085000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3223700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2326800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2112900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1961100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1766700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1577700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1467400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1414700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1296400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1341400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1190300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1130900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1056300</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>78700</v>
+      </c>
+      <c r="F45" s="3">
         <v>20500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>20500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>38600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>38600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>145200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>145200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>29800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>29800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>17800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>17800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>75800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>75800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>70300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>149000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>212500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>194100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>160900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>160600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>145000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>116400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>103400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>118800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>116900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>139800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>146300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>125600</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8995700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8995700</v>
+      </c>
+      <c r="F46" s="3">
         <v>8420100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8420100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8758100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8758100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7699400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7699400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7930700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7930700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7122700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>7122700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>8432800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8432800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>8537100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6340000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5926900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5023900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4767400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4225000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3898300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3634000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3481300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3197300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3214400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2993400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2941800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2735500</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F47" s="3">
         <v>10800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>10800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>10900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>10900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>10800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>10800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>10700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>10800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>10800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>12000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>12000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>11800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>17100</v>
-      </c>
-      <c r="R47" s="3">
-        <v>18400</v>
-      </c>
-      <c r="S47" s="3">
-        <v>18000</v>
       </c>
       <c r="T47" s="3">
         <v>18400</v>
       </c>
       <c r="U47" s="3">
+        <v>18000</v>
+      </c>
+      <c r="V47" s="3">
+        <v>18400</v>
+      </c>
+      <c r="W47" s="3">
         <v>18500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>17700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>16000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>14000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>14300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>15700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>17600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>18700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2806800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2806800</v>
+      </c>
+      <c r="F48" s="3">
         <v>2983200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2983200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2989900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2989900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3045600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3045600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3081700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3081700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3176500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3176500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2950000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2950000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2769200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1716700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1404900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1333700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1201800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>790900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>699300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>688900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>624700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>601200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>566600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>538500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>507100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>425400</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1785000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1785000</v>
+      </c>
+      <c r="F49" s="3">
         <v>978800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>978800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1995400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1995400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>965000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>965000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1935300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1935300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>897800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>897800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1838100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1838100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>885800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1242100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1268500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1247600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1222200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1202000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1142700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1135800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1120000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1099800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1117900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1074700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1060600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1050200</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,16 +4241,22 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>77800</v>
+        <v>56600</v>
       </c>
       <c r="E52" s="3">
-        <v>77800</v>
+        <v>56600</v>
       </c>
       <c r="F52" s="3">
         <v>77800</v>
@@ -4025,73 +4265,79 @@
         <v>77800</v>
       </c>
       <c r="H52" s="3">
+        <v>77800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>77800</v>
+      </c>
+      <c r="J52" s="3">
         <v>99300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>99300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>98600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>98600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>120100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>120100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>120000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>120000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>185300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>74500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>76800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>74900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>86200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>112400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>115600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>123800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>184400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>207800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>163800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>178500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>124500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13798600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13798600</v>
+      </c>
+      <c r="F54" s="3">
         <v>13429000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13429000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13894700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>13894700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12890500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12890500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13121700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>13121700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>12402000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12402000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>13430200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13430200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13315600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>9390400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>8695500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>7698100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>7296000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>6348900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5873600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5598500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5424400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5120400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5078500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>4802700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>4652700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4351400</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4032700</v>
+        <v>1749600</v>
       </c>
       <c r="E57" s="3">
-        <v>4032700</v>
+        <v>1749600</v>
       </c>
       <c r="F57" s="3">
+        <v>1817300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1817300</v>
+      </c>
+      <c r="H57" s="3">
         <v>2211000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2211000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
+        <v>1872300</v>
+      </c>
+      <c r="K57" s="3">
         <v>3871000</v>
       </c>
-      <c r="I57" s="3">
-        <v>3871000</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2012800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2012800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3391700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3391700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2040300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2040300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2093600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1723100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1441700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1131300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1009700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1085800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>946600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>863600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>829400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>765600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>797600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>673200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>706300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>696500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>523400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>523400</v>
+      </c>
+      <c r="F58" s="3">
         <v>502700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>502700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>885500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>885500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>663900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>663900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1083400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1083400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1076400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1076400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2001900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2001900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2094500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>460000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1069000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>805300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>818400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>255500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>204100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>263200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>452300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>408500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>569500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>594300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>660800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>556900</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>498500</v>
+        <v>2847400</v>
       </c>
       <c r="E59" s="3">
-        <v>498500</v>
+        <v>2847400</v>
       </c>
       <c r="F59" s="3">
+        <v>2713900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2713900</v>
+      </c>
+      <c r="H59" s="3">
         <v>2579900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2579900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>2382800</v>
+      </c>
+      <c r="K59" s="3">
         <v>384100</v>
       </c>
-      <c r="I59" s="3">
-        <v>384100</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2047500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2047500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>315400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>315400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1856700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1856700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2034300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1898300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1296200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1281100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1316900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1274600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1115500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1018600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>905400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>895700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>868900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>801900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>725100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>693800</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5120400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5120400</v>
+      </c>
+      <c r="F60" s="3">
         <v>5033800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5033800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5676400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5676400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4919000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4919000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5143600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5143600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4783500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4783500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5899000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5899000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6222300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4081400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3806900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3217700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3145000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2616000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2266200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2145400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2187200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2069700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2236000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2069500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2092200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1947200</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1050400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1050400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1256300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1256300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1409100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1409100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1446300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1446300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1596400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1596400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1765300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1765300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1726600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1726600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1763600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1241300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1141000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>929100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>830000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>540900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>560600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>573400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>551900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>501200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>495800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>467100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>407600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>333400</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>104900</v>
+      </c>
+      <c r="F62" s="3">
         <v>103700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>103700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>77800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>77800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>88000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>88000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>53900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>53900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>31500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>31500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>45700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>45700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>60300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>164800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>160600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>156900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>140500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>134600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>140000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>138900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>153500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>150500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>114100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>110600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>103600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>103800</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6351500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6351500</v>
+      </c>
+      <c r="F66" s="3">
         <v>6470600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6470600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7239300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7239300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6526900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6526900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6868800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6868800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6654400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6654400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7736500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7736500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>8110100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5487400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5108100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4303400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4115100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3291100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2966400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2857300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2891900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2720900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2845400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2646700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2603300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2384200</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6874100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6874100</v>
+      </c>
+      <c r="F72" s="3">
         <v>6481000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>6481000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>6231800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>6231800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5897100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5897100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5818300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>5818300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5298900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5298900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5239600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>5239600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4763800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3459600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3128700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2933700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2702600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2570200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2392400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2241100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2042300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1912500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1735600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1610100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1451100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1336100</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7447100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7447100</v>
+      </c>
+      <c r="F76" s="3">
         <v>6958500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6958500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6655400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6655400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6363600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6363600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6252800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6252800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5747600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5747600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5693700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5693700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5205500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3903000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3587400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3394600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3180900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3057800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2907200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2741200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2532600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2399500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2233100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2156000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2049400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1967200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,96 +6387,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6141,47 +6531,53 @@
       <c r="P81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S81" s="3">
         <v>469200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>331600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>329900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>285000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>297700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>254700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>266000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>204400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>231900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>177000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>195700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>158700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>164100</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,80 +6607,82 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>48800</v>
+        <v>110100</v>
       </c>
       <c r="E83" s="3">
-        <v>48800</v>
+        <v>110100</v>
       </c>
       <c r="F83" s="3">
+        <v>69900</v>
+      </c>
+      <c r="G83" s="3">
+        <v>69900</v>
+      </c>
+      <c r="H83" s="3">
         <v>115500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>115500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>80400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>80400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>105300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>105300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>75100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>75100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>92300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>92300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>64000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>232000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>172100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>169700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>155800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>123100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>118100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>110200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>102000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6294,8 +6692,14 @@
       <c r="AC83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>492300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>492300</v>
+      </c>
+      <c r="F89" s="3">
         <v>630000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>630000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>359600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>359600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>746400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>746400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>387500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>387500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>705100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>705100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>346900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>346900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>586400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>945300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>213800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>796000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-71700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>602000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>191600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>493700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>104600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>458300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>125300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>275900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>59300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,80 +7263,82 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-96600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-96600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-47900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-47900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-95800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-95800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-49900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-49900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-146000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-146000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-104800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-104800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-175800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-421400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-195700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-286900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-253000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-173700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-85400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-131800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-71800</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>10</v>
       </c>
@@ -6906,8 +7348,14 @@
       <c r="AC91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-107300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-107300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-150200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-150200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-109000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-109000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-185800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-185800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-117300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-117300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-206500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-206500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-182900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-182900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-240900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-404300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-176000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-262800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-305700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-284100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-139600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-212500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-134100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-158800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-127600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-146000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-174900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-123100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,80 +7652,82 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>155400</v>
+      </c>
+      <c r="F96" s="3">
         <v>286300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>286300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H96" s="3">
+        <v>139100</v>
+      </c>
+      <c r="I96" s="3">
+        <v>139100</v>
+      </c>
+      <c r="J96" s="3">
         <v>243100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>243100</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N96" s="3">
         <v>218400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>218400</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R96" s="3">
         <v>112200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-124900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-136700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-106000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-117600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-89600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-93800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-65500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-70800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -7269,8 +7737,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-282400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-282400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-451700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-451700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-88900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-88900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-543000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-543000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-123400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-123400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-778300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-778300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-122600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-122600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-264900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-771400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>273300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-322700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>485400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-62300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-43600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-246100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>29100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-222200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-59800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>152700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-217300</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-14700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-14700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-10100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-10100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>13800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>13800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-13400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-13400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-20100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-20100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>49400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-8100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-4300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-6300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-14800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-8700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>12500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>13200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>105800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>105800</v>
+      </c>
+      <c r="F102" s="3">
         <v>34700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>34700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>188000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>188000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>136700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>136700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-265900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-265900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>28100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>28100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>77400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-181000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>303100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>206300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>101700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>240800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>47600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>12900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>59200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-26900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>51300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>31700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>40600</v>
       </c>
     </row>
